--- a/dataset/01.w_Defects/uninit_memory_access.xlsx
+++ b/dataset/01.w_Defects/uninit_memory_access.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define ERROR 0x1 typedef struct { int arr[MAX]; int a; int b; int c; } uninit_memory_access_007_s_001; long ** uninit_memory_access_009_doubleptr_gbl; volatile uninit_memory_access_010_s_001 *uninit_memory_access_010_s_001_arr_gbl; enum {max_buffer = 24}; typedef enum { true=1, false=0} bool; extern volatile int vflag; void uninit_memory_access_007 () { uninit_memory_access_007_s_001 st; uninit_memory_access_007_func_001(&amp;st); uninit_memory_access_007_func_002(&amp;st); uninit_memory_access_007_func_003(&amp;st); uninit_memory_access_007_func_004(st.a); } void uninit_memory_access_007_func_001(uninit_memory_access_007_s_001* st) { memset(st-&gt;arr, 0, 1); st-&gt;a = 1; } void uninit_memory_access_007_func_003(uninit_memory_access_007_s_001 *st) { st-&gt;b = 10; st-&gt;c =20; } void uninit_memory_access_007_func_004(int num) { int temp; if(num != 0) { temp = num; } } void uninit_memory_access_007_func_002(uninit_memory_access_007_s_001 *st) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { temp += st-&gt;arr[i];/*Tool should detect this line as error*/ /*ERROR:Uninitialized Memory Access*/ } }</t>
+          <t>#define MAX 10 #define ERROR 0x1 typedef struct { int arr[MAX]; int a; int b; int c; } uninit_memory_access_007_s_001; long ** uninit_memory_access_009_doubleptr_gbl; volatile uninit_memory_access_010_s_001 *uninit_memory_access_010_s_001_arr_gbl; enum {max_buffer = 24}; typedef enum { true=1, false=0} bool; extern volatile int vflag; void uninit_memory_access_007 () { uninit_memory_access_007_s_001 st; uninit_memory_access_007_func_001(&amp;st); uninit_memory_access_007_func_002(&amp;st); uninit_memory_access_007_func_003(&amp;st); uninit_memory_access_007_func_004(st.a); } void uninit_memory_access_007_func_001(uninit_memory_access_007_s_001* st) { memset(st-&gt;arr, 0, 1); st-&gt;a = 1; } void uninit_memory_access_007_func_003(uninit_memory_access_007_s_001 *st) { st-&gt;b = 10; st-&gt;c =20; } void uninit_memory_access_007_func_002(uninit_memory_access_007_s_001 *st) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { temp += st-&gt;arr[i];/*Tool should detect this line as error*/ /*ERROR:Uninitialized Memory Access*/ } } void uninit_memory_access_007_func_004(int num) { int temp; if(num != 0) { temp = num; } }</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
